--- a/notes/SensitivityTraits_Birds.xlsx
+++ b/notes/SensitivityTraits_Birds.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\dev\eryn\envSens\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9758307-BD0F-4272-9769-22822C1B42E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4991F4A2-7F33-445F-98AB-CFD2F5B5C4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9760" yWindow="-10910" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8254AB1E-5A4B-4BBA-84A2-E1EDCEC08EF2}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="1" xr2:uid="{8254AB1E-5A4B-4BBA-84A2-E1EDCEC08EF2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sensitivity_v1 (modified)" sheetId="2" r:id="rId1"/>
-    <sheet name="Sensitivity_v2" sheetId="5" r:id="rId2"/>
-    <sheet name="Habitat-IUCN" sheetId="3" r:id="rId3"/>
-    <sheet name="Threat-IUCN" sheetId="4" r:id="rId4"/>
+    <sheet name="Sensitivity_v1_original" sheetId="2" r:id="rId1"/>
+    <sheet name="Sensitivity_v2_poolall" sheetId="5" r:id="rId2"/>
+    <sheet name="Sensitivity_simple" sheetId="7" r:id="rId3"/>
+    <sheet name="Habitat-IUCN" sheetId="3" r:id="rId4"/>
+    <sheet name="Threat-IUCN" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="227">
   <si>
     <t>Condition</t>
   </si>
@@ -54,15 +55,15 @@
     <t>Full migrant</t>
   </si>
   <si>
-    <t>Partial migrant</t>
-  </si>
-  <si>
     <t>simpson index</t>
   </si>
   <si>
     <t>1 - simpson index</t>
   </si>
   <si>
+    <t>Habitat breadth</t>
+  </si>
+  <si>
     <t>log(EOO)</t>
   </si>
   <si>
@@ -75,9 +76,6 @@
     <t>Trait</t>
   </si>
   <si>
-    <t>Non migrant</t>
-  </si>
-  <si>
     <t>Definition</t>
   </si>
   <si>
@@ -114,12 +112,6 @@
     <t>Garnett et al. 2015</t>
   </si>
   <si>
-    <t>Taxa in which all individuals leave the breeding location after breeding is complete.</t>
-  </si>
-  <si>
-    <t>Not full migrant nor partial migrant.</t>
-  </si>
-  <si>
     <t>Tobias &amp; Pigot 2019</t>
   </si>
   <si>
@@ -129,9 +121,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Taxa in which some individuals regularly move away from breeding areas after nesting but some remain behind all year.</t>
-  </si>
-  <si>
     <t>The number of major habitat used.</t>
   </si>
   <si>
@@ -165,18 +154,6 @@
     <t>1 - scaled value</t>
   </si>
   <si>
-    <t xml:space="preserve">Breed in both agriculture and urban landscape and feed in one/both of them; Feed in both of them and breed in one/both of them. </t>
-  </si>
-  <si>
-    <t>Breed in either agriculture or urban landscape.</t>
-  </si>
-  <si>
-    <t>Feed in either agriculture or urban landscape.</t>
-  </si>
-  <si>
-    <t>Do not breed or feed in agriculture or urban landscape.</t>
-  </si>
-  <si>
     <t>Species capable of utilise a non-trivial proportion of human-modified environments show reduced sensitivity to habitat disturbance and lower extinction risk.</t>
   </si>
   <si>
@@ -612,21 +589,6 @@
     <t>Suitable = 3; Marginal = 1; Resident = 1; Breeding = 0.5; Non-breeding = 0.5</t>
   </si>
   <si>
-    <t>Scored the artificial habitat subtypes using a habitat lookup table that is based on the degree of degradation</t>
-  </si>
-  <si>
-    <t>Non artificial habitat</t>
-  </si>
-  <si>
-    <t>Almost no vegetation cover</t>
-  </si>
-  <si>
-    <t>Native vegetation cover or aquatic system remain</t>
-  </si>
-  <si>
-    <t>Non native vegetation cover and man-made aquatic system</t>
-  </si>
-  <si>
     <t>Altitudinal migrant</t>
   </si>
   <si>
@@ -658,13 +620,116 @@
   </si>
   <si>
     <t>non-raptors</t>
+  </si>
+  <si>
+    <t>Raptors are apex or near-apex predators with large home ranges and sensitivity to prey availability, and are also preferentially reported by observers.</t>
+  </si>
+  <si>
+    <t>Scored the artificial habitat subtypes using a habitat lookup table that is based on the degree of degradation.
+Non artificial habitat = 0; Native vegetation cover or aquatic system remain =1; Non native vegetation cover and man-made aquatic system = 2; Almost no vegetation cover = 3</t>
+  </si>
+  <si>
+    <t>Artificial habitat breadth</t>
+  </si>
+  <si>
+    <t>ln(score)</t>
+  </si>
+  <si>
+    <t>Raw_score</t>
+  </si>
+  <si>
+    <t>Otherwise</t>
+  </si>
+  <si>
+    <t>Diet breadth</t>
+  </si>
+  <si>
+    <t>Caculated Simpson diversity index across types and proportioins of diet</t>
+  </si>
+  <si>
+    <t>Caculated Simpson diversity index across types and proportioins of habitat use</t>
+  </si>
+  <si>
+    <t>Range size</t>
+  </si>
+  <si>
+    <t>Scaled using scale_aubird_minmax() on the log transformed Extent of Occurrance</t>
+  </si>
+  <si>
+    <t>1 - scaled_value</t>
+  </si>
+  <si>
+    <t>Restricted Range</t>
+  </si>
+  <si>
+    <t>Global range size &lt; 50,000 km2 (1)</t>
+  </si>
+  <si>
+    <t>Global range size &gt; 50,000 km2 (0)</t>
+  </si>
+  <si>
+    <t>Scaled using scale_aubird_minmax() on nature log transformed generation length</t>
+  </si>
+  <si>
+    <t>ln(genlength)</t>
+  </si>
+  <si>
+    <t>scaled_value</t>
+  </si>
+  <si>
+    <t>(breedadapt + feedadapt) &gt; 2</t>
+  </si>
+  <si>
+    <t>breedadapt &gt; 0</t>
+  </si>
+  <si>
+    <t>feedadapt &gt; 0</t>
+  </si>
+  <si>
+    <t>(breedadapt + feedadapt) == 0</t>
+  </si>
+  <si>
+    <t>Generation Length</t>
+  </si>
+  <si>
+    <t>Literature reference</t>
+  </si>
+  <si>
+    <t>Bird et al. 2020</t>
+  </si>
+  <si>
+    <t>BIRDBASE (Şekercioğlu et al. 2025)</t>
+  </si>
+  <si>
+    <t>Olah et al. 2024</t>
+  </si>
+  <si>
+    <t>Cassey et al. 2004; Blackburn, Cassey, and Lockwood 2009; Tobias and Pigot 2019; Bird et al. 2020</t>
+  </si>
+  <si>
+    <t>Cassey et al. 2004; Blackburn, Cassey, and Lockwood 2009</t>
+  </si>
+  <si>
+    <t>Partial migrant and Altitudinal/elevational migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yearly, regular, seasonal (larger scale), and/or long-distance movement. </t>
+  </si>
+  <si>
+    <t>Nomadic and non-migrant</t>
+  </si>
+  <si>
+    <t>Partial and Altitudinal migrant</t>
+  </si>
+  <si>
+    <t>Long-distance migrant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -686,6 +751,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -701,7 +781,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -729,11 +809,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -750,13 +872,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -764,11 +883,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -781,16 +897,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -803,17 +913,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1149,456 +1295,389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D0C682-9163-4871-BD3A-6A5531D316E6}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.23046875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="40.84375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.4609375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="18.3828125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="37.3828125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.84375" style="10" customWidth="1"/>
-    <col min="8" max="9" width="12.84375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.84375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.23046875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="33.921875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="19.15234375" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.53515625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="38.61328125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="14.69140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="41.07421875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17.4609375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.3828125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="37.3828125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="12.84375" style="9" customWidth="1"/>
+    <col min="12" max="13" width="12.84375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="14.84375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="21" t="s">
+      <c r="B1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="22" t="s">
+      <c r="C1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="87.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="D1" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+    </row>
+    <row r="2" spans="1:14" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A2" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" s="38">
+        <v>3</v>
+      </c>
+      <c r="G2" s="38">
+        <v>1</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+    </row>
+    <row r="3" spans="1:14" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" s="38">
+        <v>2</v>
+      </c>
+      <c r="G3" s="38">
+        <v>0.67</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="38">
+        <v>1</v>
+      </c>
+      <c r="G4" s="38">
+        <v>0.33</v>
+      </c>
+      <c r="H4" s="22"/>
+      <c r="I4" s="20"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A5" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A6" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.4">
+      <c r="A7" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C7" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="24">
-        <v>1</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A3" s="20"/>
-      <c r="B3" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="24">
-        <v>1</v>
-      </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-    </row>
-    <row r="4" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A4" s="20"/>
-      <c r="B4" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="24">
-        <v>1</v>
-      </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-    </row>
-    <row r="5" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="C8" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" s="38">
+        <v>0</v>
+      </c>
+      <c r="G8" s="38">
+        <v>0</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" s="38">
+        <v>1</v>
+      </c>
+      <c r="G9" s="38">
+        <v>1</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="87.45" x14ac:dyDescent="0.4">
+      <c r="A10" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-    </row>
-    <row r="6" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A6" s="20"/>
-      <c r="B6" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="58.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="20" t="s">
+      <c r="D10" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2">
+      <c r="B11" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="38">
+        <v>0</v>
+      </c>
+      <c r="G11" s="38">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="38">
+        <v>1</v>
+      </c>
+      <c r="G12" s="38">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="38">
         <v>2</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2">
+      <c r="G13" s="38">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F14" s="38">
         <v>3</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A12" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A13" s="20"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="2">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="20"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="20"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="12"/>
+      <c r="G14" s="38">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
+  <mergeCells count="16">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="H7:H8"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D11:D14"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1614,477 +1693,509 @@
     <col min="2" max="2" width="27.765625" customWidth="1"/>
     <col min="3" max="3" width="31.765625" customWidth="1"/>
     <col min="4" max="4" width="28.53515625" customWidth="1"/>
-    <col min="5" max="5" width="25.84375" customWidth="1"/>
+    <col min="5" max="5" width="31.765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.53515625" customWidth="1"/>
-    <col min="7" max="7" width="15" style="11" customWidth="1"/>
-    <col min="8" max="8" width="14.4609375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="13.84375" style="19" customWidth="1"/>
+    <col min="7" max="7" width="12.53515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.23046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.84375" style="18" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="22" t="s">
+      <c r="D1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="E1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="B2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="25">
+        <v>0.33</v>
+      </c>
+      <c r="I2" s="25">
+        <f>H2/5</f>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="22"/>
+      <c r="B3" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="I3" s="20">
+        <f t="shared" ref="I3:I19" si="0">H3/5</f>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="27">
+        <v>0.33</v>
+      </c>
+      <c r="I4" s="27">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A3" s="20"/>
-      <c r="B3" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="24"/>
-    </row>
-    <row r="4" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A4" s="20"/>
-      <c r="B4" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="24"/>
-    </row>
-    <row r="5" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="F5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="20">
         <v>0.6</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="24"/>
-    </row>
-    <row r="6" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A6" s="20"/>
-      <c r="B6" s="25" t="s">
-        <v>178</v>
+      <c r="I5" s="20">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27" t="s">
+        <v>170</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
-      <c r="E6" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="E6" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="27">
         <v>0.4</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="2" t="s">
-        <v>31</v>
+      <c r="I6" s="27">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="24" t="s">
+      <c r="A7" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="C7" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="29">
+        <v>1</v>
+      </c>
+      <c r="I7" s="29">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="20">
-        <v>1</v>
-      </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="2">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="25" t="s">
+      <c r="B8" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="2">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
+      <c r="F8" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="24">
+        <v>1</v>
+      </c>
+      <c r="I8" s="24">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" ht="29.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" ht="96.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
-      <c r="F11" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A12" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="25">
         <v>3</v>
       </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A12" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="26" t="s">
+      <c r="H12" s="24">
+        <v>0.33</v>
+      </c>
+      <c r="I12" s="24">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="G13" s="20">
         <v>2</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3</v>
-      </c>
-      <c r="H12" s="20">
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="G14" s="20">
+        <v>1</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" spans="1:10" ht="48.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22">
         <v>0.33</v>
       </c>
-      <c r="I12" s="25"/>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A13" s="20"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="G13" s="2">
-        <v>2</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="2">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A14" s="20"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="20"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="2">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="48.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20"/>
-      <c r="B15" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="I15" s="22">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="54.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" ht="87.45" x14ac:dyDescent="0.4">
+      <c r="A17" s="22"/>
+      <c r="B17" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="I15" s="25"/>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="54.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A17" s="20"/>
-      <c r="B17" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" s="2">
+      <c r="D17" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="20">
         <f>0.33/2</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="I17" s="25"/>
-      <c r="J17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A18" s="20"/>
-      <c r="B18" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="9">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
+      <c r="I17" s="20">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="39.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="22">
         <f>0.33/2</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="I18" s="25"/>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="20"/>
+      <c r="I18" s="22">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="50.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
       <c r="B19" s="26"/>
-      <c r="C19" s="20"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="26"/>
       <c r="E19" s="30" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G19" s="31">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="35">
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J15:J16"/>
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="H12:H14"/>
     <mergeCell ref="H15:H16"/>
@@ -2092,6 +2203,7 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="D18:D19"/>
+    <mergeCell ref="H18:H19"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="C12:C14"/>
@@ -2110,11 +2222,554 @@
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="D8:D11"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72661712-454A-491A-B2EE-1F8560915A81}">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.84375" customWidth="1"/>
+    <col min="4" max="4" width="19.07421875" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="20.61328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.23046875" customWidth="1"/>
+    <col min="8" max="8" width="11.921875" customWidth="1"/>
+    <col min="9" max="9" width="11.84375" customWidth="1"/>
+    <col min="10" max="10" width="13.3046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="25">
+        <v>0.33</v>
+      </c>
+      <c r="I2" s="25">
+        <f>H2/5</f>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="22"/>
+      <c r="B3" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="I3" s="20">
+        <f t="shared" ref="I3:I18" si="0">H3/5</f>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="27">
+        <v>0.33</v>
+      </c>
+      <c r="I4" s="27">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0.6</v>
+      </c>
+      <c r="I5" s="20">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="27">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="27">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="29">
+        <v>1</v>
+      </c>
+      <c r="I7" s="29">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="24">
+        <v>1</v>
+      </c>
+      <c r="I8" s="24">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+    </row>
+    <row r="12" spans="1:10" ht="116.6" x14ac:dyDescent="0.4">
+      <c r="A12" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="25">
+        <v>3</v>
+      </c>
+      <c r="H12" s="24">
+        <v>0.33</v>
+      </c>
+      <c r="I12" s="24">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="87.45" x14ac:dyDescent="0.4">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="20">
+        <v>2</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:10" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="20">
+        <v>1</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22">
+        <v>0.33</v>
+      </c>
+      <c r="I15" s="22">
+        <f t="shared" si="0"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A17" s="22"/>
+      <c r="B17" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="20">
+        <f>0.33/2</f>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="I17" s="20">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="22">
+        <f>0.33/2</f>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="I18" s="22">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" s="31">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EBEF19-CD3A-4E0D-8B18-E7C3DB223DB4}">
   <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -2126,23 +2781,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>173</v>
+      <c r="A1" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -2152,14 +2807,14 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>28</v>
+      <c r="C2" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2172,14 +2827,14 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>28</v>
+      <c r="C3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2192,14 +2847,14 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>28</v>
+      <c r="C4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2212,14 +2867,14 @@
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>28</v>
+      <c r="C5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2232,14 +2887,14 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>28</v>
+      <c r="C6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2252,14 +2907,14 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>28</v>
+      <c r="C7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2272,14 +2927,14 @@
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>28</v>
+      <c r="C8" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2292,14 +2947,14 @@
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>28</v>
+      <c r="E9" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2312,14 +2967,14 @@
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>28</v>
+      <c r="C10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2332,14 +2987,14 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>28</v>
+      <c r="C11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2352,14 +3007,14 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>28</v>
+      <c r="C12" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2372,14 +3027,14 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>28</v>
+      <c r="C13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2392,14 +3047,14 @@
       <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>28</v>
+      <c r="C14" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2412,14 +3067,14 @@
       <c r="B15">
         <v>3</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>28</v>
+      <c r="C15" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2432,14 +3087,14 @@
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>28</v>
+      <c r="C16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2452,14 +3107,14 @@
       <c r="B17">
         <v>5</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>28</v>
+      <c r="D17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2472,14 +3127,14 @@
       <c r="B18">
         <v>6</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>28</v>
+      <c r="C18" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2492,14 +3147,14 @@
       <c r="B19">
         <v>7</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>28</v>
+      <c r="C19" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2512,14 +3167,14 @@
       <c r="B20">
         <v>8</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>28</v>
+      <c r="C20" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2532,14 +3187,14 @@
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>28</v>
+      <c r="C21" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2552,14 +3207,14 @@
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>28</v>
+      <c r="C22" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2572,14 +3227,14 @@
       <c r="B23">
         <v>3</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>28</v>
+      <c r="C23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2592,14 +3247,14 @@
       <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>28</v>
+      <c r="C24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2612,14 +3267,14 @@
       <c r="B25">
         <v>5</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>28</v>
+      <c r="C25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2632,14 +3287,14 @@
       <c r="B26">
         <v>6</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>28</v>
+      <c r="C26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2652,14 +3307,14 @@
       <c r="B27">
         <v>7</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>28</v>
+      <c r="C27" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2672,14 +3327,14 @@
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>28</v>
+      <c r="C28" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2692,14 +3347,14 @@
       <c r="B29">
         <v>2</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>28</v>
+      <c r="C29" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -2712,14 +3367,14 @@
       <c r="B30">
         <v>3</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>28</v>
+      <c r="C30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2732,14 +3387,14 @@
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>28</v>
+      <c r="C31" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -2752,14 +3407,14 @@
       <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>28</v>
+      <c r="C32" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2772,14 +3427,14 @@
       <c r="B33">
         <v>6</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>28</v>
+      <c r="C33" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2792,14 +3447,14 @@
       <c r="B34">
         <v>7</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>28</v>
+      <c r="C34" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2812,14 +3467,14 @@
       <c r="B35">
         <v>8</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>28</v>
+      <c r="E35" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2832,14 +3487,14 @@
       <c r="B36">
         <v>9</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>28</v>
+      <c r="C36" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2852,14 +3507,14 @@
       <c r="B37">
         <v>10</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>28</v>
+      <c r="C37" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2872,14 +3527,14 @@
       <c r="B38">
         <v>11</v>
       </c>
-      <c r="C38" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>28</v>
+      <c r="C38" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2892,14 +3547,14 @@
       <c r="B39">
         <v>12</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>28</v>
+      <c r="C39" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2912,14 +3567,14 @@
       <c r="B40">
         <v>13</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>28</v>
+      <c r="C40" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2932,14 +3587,14 @@
       <c r="B41">
         <v>14</v>
       </c>
-      <c r="C41" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>28</v>
+      <c r="C41" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2952,14 +3607,14 @@
       <c r="B42">
         <v>15</v>
       </c>
-      <c r="C42" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>28</v>
+      <c r="C42" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2972,14 +3627,14 @@
       <c r="B43">
         <v>16</v>
       </c>
-      <c r="C43" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>28</v>
+      <c r="C43" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2992,14 +3647,14 @@
       <c r="B44">
         <v>17</v>
       </c>
-      <c r="C44" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>28</v>
+      <c r="C44" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -3012,14 +3667,14 @@
       <c r="B45">
         <v>18</v>
       </c>
-      <c r="C45" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>28</v>
+      <c r="C45" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3032,14 +3687,14 @@
       <c r="B46">
         <v>1</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>28</v>
+      <c r="C46" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3052,14 +3707,14 @@
       <c r="B47">
         <v>1</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>28</v>
+      <c r="C47" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -3072,14 +3727,14 @@
       <c r="B48">
         <v>2</v>
       </c>
-      <c r="C48" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>28</v>
+      <c r="C48" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -3092,14 +3747,14 @@
       <c r="B49">
         <v>1</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>28</v>
+      <c r="C49" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -3112,14 +3767,14 @@
       <c r="B50">
         <v>2</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>28</v>
+      <c r="C50" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -3132,14 +3787,14 @@
       <c r="B51">
         <v>3</v>
       </c>
-      <c r="C51" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>28</v>
+      <c r="C51" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -3152,14 +3807,14 @@
       <c r="B52">
         <v>1</v>
       </c>
-      <c r="C52" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>28</v>
+      <c r="C52" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -3172,14 +3827,14 @@
       <c r="B53">
         <v>2</v>
       </c>
-      <c r="C53" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>28</v>
+      <c r="C53" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3192,14 +3847,14 @@
       <c r="B54">
         <v>3</v>
       </c>
-      <c r="C54" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>28</v>
+      <c r="C54" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3212,14 +3867,14 @@
       <c r="B55">
         <v>4</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>28</v>
+      <c r="C55" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -3232,14 +3887,14 @@
       <c r="B56">
         <v>5</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>28</v>
+      <c r="C56" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3252,14 +3907,14 @@
       <c r="B57">
         <v>6</v>
       </c>
-      <c r="C57" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>28</v>
+      <c r="C57" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -3272,14 +3927,14 @@
       <c r="B58">
         <v>7</v>
       </c>
-      <c r="C58" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>28</v>
+      <c r="C58" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3292,14 +3947,14 @@
       <c r="B59">
         <v>8</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E59" s="15" t="s">
-        <v>111</v>
+      <c r="E59" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3312,14 +3967,14 @@
       <c r="B60">
         <v>9</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D60" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>112</v>
+      <c r="E60" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3332,14 +3987,14 @@
       <c r="B61">
         <v>10</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D61" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>113</v>
+      <c r="E61" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3352,14 +4007,14 @@
       <c r="B62">
         <v>11</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>114</v>
+      <c r="E62" s="13" t="s">
+        <v>106</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3372,14 +4027,14 @@
       <c r="B63">
         <v>12</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D63" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>115</v>
+      <c r="E63" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3392,14 +4047,14 @@
       <c r="B64">
         <v>13</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>116</v>
+      <c r="E64" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3412,14 +4067,14 @@
       <c r="B65">
         <v>14</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>28</v>
+      <c r="C65" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3432,14 +4087,14 @@
       <c r="B66">
         <v>15</v>
       </c>
-      <c r="C66" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>28</v>
+      <c r="C66" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3452,14 +4107,14 @@
       <c r="B67">
         <v>1</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E67" s="15" t="s">
-        <v>28</v>
+      <c r="C67" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3472,14 +4127,14 @@
       <c r="B68">
         <v>2</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>28</v>
+      <c r="C68" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3492,14 +4147,14 @@
       <c r="B69">
         <v>3</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>28</v>
+      <c r="C69" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3512,14 +4167,14 @@
       <c r="B70">
         <v>4</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>28</v>
+      <c r="C70" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3532,14 +4187,14 @@
       <c r="B71">
         <v>1</v>
       </c>
-      <c r="C71" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>126</v>
+      <c r="C71" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3552,14 +4207,14 @@
       <c r="B72">
         <v>2</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>127</v>
+      <c r="C72" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>119</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3572,14 +4227,14 @@
       <c r="B73">
         <v>3</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>28</v>
+      <c r="C73" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -3592,14 +4247,14 @@
       <c r="B74">
         <v>4</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>28</v>
+      <c r="C74" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3612,14 +4267,14 @@
       <c r="B75">
         <v>5</v>
       </c>
-      <c r="C75" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>28</v>
+      <c r="C75" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3632,14 +4287,14 @@
       <c r="B76">
         <v>6</v>
       </c>
-      <c r="C76" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>28</v>
+      <c r="C76" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -3652,14 +4307,14 @@
       <c r="B77">
         <v>7</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D77" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>28</v>
+      <c r="E77" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -3672,14 +4327,14 @@
       <c r="B78">
         <v>1</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" s="15" t="s">
-        <v>28</v>
+      <c r="C78" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3692,14 +4347,14 @@
       <c r="B79">
         <v>2</v>
       </c>
-      <c r="C79" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E79" s="15" t="s">
-        <v>28</v>
+      <c r="C79" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3712,14 +4367,14 @@
       <c r="B80">
         <v>3</v>
       </c>
-      <c r="C80" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>28</v>
+      <c r="C80" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3732,14 +4387,14 @@
       <c r="B81">
         <v>4</v>
       </c>
-      <c r="C81" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E81" s="15" t="s">
-        <v>28</v>
+      <c r="C81" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3752,14 +4407,14 @@
       <c r="B82">
         <v>5</v>
       </c>
-      <c r="C82" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>28</v>
+      <c r="C82" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3772,14 +4427,14 @@
       <c r="B83">
         <v>6</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>28</v>
+      <c r="C83" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -3792,14 +4447,14 @@
       <c r="B84">
         <v>7</v>
       </c>
-      <c r="C84" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>28</v>
+      <c r="C84" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3812,14 +4467,14 @@
       <c r="B85">
         <v>1</v>
       </c>
-      <c r="C85" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>28</v>
+      <c r="C85" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -3832,14 +4487,14 @@
       <c r="B86">
         <v>2</v>
       </c>
-      <c r="C86" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>28</v>
+      <c r="C86" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3852,14 +4507,14 @@
       <c r="B87">
         <v>3</v>
       </c>
-      <c r="C87" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>28</v>
+      <c r="C87" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3872,14 +4527,14 @@
       <c r="B88">
         <v>4</v>
       </c>
-      <c r="C88" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E88" s="15" t="s">
-        <v>28</v>
+      <c r="C88" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3892,14 +4547,14 @@
       <c r="B89">
         <v>5</v>
       </c>
-      <c r="C89" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>28</v>
+      <c r="C89" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3912,376 +4567,376 @@
       <c r="B90">
         <v>1</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A91" s="15">
+        <v>14</v>
+      </c>
+      <c r="B91" s="15">
+        <v>2</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A92" s="15">
+        <v>14</v>
+      </c>
+      <c r="B92" s="15">
+        <v>3</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" s="15">
+        <v>14</v>
+      </c>
+      <c r="B93" s="15">
+        <v>4</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="E93" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A94" s="15">
+        <v>14</v>
+      </c>
+      <c r="B94" s="15">
+        <v>5</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" s="15">
+        <v>14</v>
+      </c>
+      <c r="B95" s="15">
+        <v>6</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" s="15">
+        <v>15</v>
+      </c>
+      <c r="B96" s="15">
+        <v>1</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="E96" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" s="15">
+        <v>15</v>
+      </c>
+      <c r="B97" s="15">
+        <v>2</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D97" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E90" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A91" s="17">
-        <v>14</v>
-      </c>
-      <c r="B91" s="17">
+      <c r="E97" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" s="15">
+        <v>15</v>
+      </c>
+      <c r="B98" s="15">
+        <v>3</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="13">
         <v>2</v>
       </c>
-      <c r="C91" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="E91" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F91" s="15">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" s="15">
+        <v>15</v>
+      </c>
+      <c r="B99" s="15">
+        <v>4</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" s="15">
+        <v>15</v>
+      </c>
+      <c r="B100" s="15">
+        <v>5</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" s="15">
+        <v>15</v>
+      </c>
+      <c r="B101" s="15">
+        <v>6</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A92" s="17">
-        <v>14</v>
-      </c>
-      <c r="B92" s="17">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A102" s="15">
+        <v>15</v>
+      </c>
+      <c r="B102" s="15">
+        <v>7</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" s="15">
+        <v>15</v>
+      </c>
+      <c r="B103" s="15">
+        <v>8</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E103" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" s="15">
+        <v>15</v>
+      </c>
+      <c r="B104" s="15">
+        <v>9</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E104" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" s="15">
+        <v>15</v>
+      </c>
+      <c r="B105" s="15">
+        <v>10</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="E105" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" s="13">
         <v>3</v>
       </c>
-      <c r="C92" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E92" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F92" s="15">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" s="15">
+        <v>15</v>
+      </c>
+      <c r="B106" s="15">
+        <v>11</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" s="15">
+        <v>15</v>
+      </c>
+      <c r="B107" s="15">
+        <v>12</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A93" s="17">
-        <v>14</v>
-      </c>
-      <c r="B93" s="17">
-        <v>4</v>
-      </c>
-      <c r="C93" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D93" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E93" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F93" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A94" s="17">
-        <v>14</v>
-      </c>
-      <c r="B94" s="17">
-        <v>5</v>
-      </c>
-      <c r="C94" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E94" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F94" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A95" s="17">
-        <v>14</v>
-      </c>
-      <c r="B95" s="17">
-        <v>6</v>
-      </c>
-      <c r="C95" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D95" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E95" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F95" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A96" s="17">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" s="15">
         <v>15</v>
       </c>
-      <c r="B96" s="17">
-        <v>1</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D96" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F96" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A97" s="17">
-        <v>15</v>
-      </c>
-      <c r="B97" s="17">
-        <v>2</v>
-      </c>
-      <c r="C97" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D97" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="E97" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F97" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A98" s="17">
-        <v>15</v>
-      </c>
-      <c r="B98" s="17">
-        <v>3</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D98" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E98" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F98" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A99" s="17">
-        <v>15</v>
-      </c>
-      <c r="B99" s="17">
-        <v>4</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E99" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F99" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A100" s="17">
-        <v>15</v>
-      </c>
-      <c r="B100" s="17">
-        <v>5</v>
-      </c>
-      <c r="C100" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D100" s="18" t="s">
+      <c r="B108" s="15">
+        <v>13</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D108" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="E100" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F100" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A101" s="17">
-        <v>15</v>
-      </c>
-      <c r="B101" s="17">
-        <v>6</v>
-      </c>
-      <c r="C101" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D101" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="E101" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F101" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A102" s="17">
-        <v>15</v>
-      </c>
-      <c r="B102" s="17">
-        <v>7</v>
-      </c>
-      <c r="C102" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D102" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E102" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F102" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A103" s="17">
-        <v>15</v>
-      </c>
-      <c r="B103" s="17">
-        <v>8</v>
-      </c>
-      <c r="C103" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D103" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F103" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A104" s="17">
-        <v>15</v>
-      </c>
-      <c r="B104" s="17">
-        <v>9</v>
-      </c>
-      <c r="C104" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D104" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="E104" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F104" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A105" s="17">
-        <v>15</v>
-      </c>
-      <c r="B105" s="17">
-        <v>10</v>
-      </c>
-      <c r="C105" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D105" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F105" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A106" s="17">
-        <v>15</v>
-      </c>
-      <c r="B106" s="17">
-        <v>11</v>
-      </c>
-      <c r="C106" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D106" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="E106" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F106" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A107" s="17">
-        <v>15</v>
-      </c>
-      <c r="B107" s="17">
-        <v>12</v>
-      </c>
-      <c r="C107" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E107" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F107" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A108" s="17">
-        <v>15</v>
-      </c>
-      <c r="B108" s="17">
-        <v>13</v>
-      </c>
-      <c r="C108" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D108" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E108" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F108" s="15">
+      <c r="E108" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="13">
         <v>1</v>
       </c>
     </row>
@@ -4292,14 +4947,14 @@
       <c r="B109">
         <v>1</v>
       </c>
-      <c r="C109" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D109" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E109" s="15" t="s">
-        <v>28</v>
+      <c r="C109" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -4312,14 +4967,14 @@
       <c r="B110">
         <v>1</v>
       </c>
-      <c r="C110" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>28</v>
+      <c r="C110" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -4332,14 +4987,14 @@
       <c r="B111">
         <v>1</v>
       </c>
-      <c r="C111" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E111" s="15" t="s">
-        <v>28</v>
+      <c r="C111" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -4350,7 +5005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0AEA4A-2460-4D41-A208-D4C0A1C8BDAF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
